--- a/sample-data/PMS_cycle_FY26-H1.xlsx
+++ b/sample-data/PMS_cycle_FY26-H1.xlsx
@@ -454,7 +454,7 @@
         <v>Y</v>
       </c>
       <c r="D2" t="str">
-        <v>2025-04-06</v>
+        <v>2025-04-07</v>
       </c>
       <c r="E2" t="str">
         <v>Y</v>
@@ -463,13 +463,13 @@
         <v>Y</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H2" t="str">
         <v>1-5</v>
       </c>
       <c r="I2" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="J2" t="str">
         <v>High</v>
@@ -498,7 +498,7 @@
         <v>Y</v>
       </c>
       <c r="D3" t="str">
-        <v>2025-04-03</v>
+        <v>2025-04-04</v>
       </c>
       <c r="E3" t="str">
         <v>Y</v>
@@ -507,19 +507,19 @@
         <v>Y</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3" t="str">
         <v>1-5</v>
       </c>
       <c r="I3" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="J3" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K3" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L3" t="str">
         <v>N</v>
@@ -542,7 +542,7 @@
         <v>Y</v>
       </c>
       <c r="D4" t="str">
-        <v>2025-04-02</v>
+        <v>2025-04-06</v>
       </c>
       <c r="E4" t="str">
         <v>Y</v>
@@ -551,7 +551,7 @@
         <v>Y</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H4" t="str">
         <v>1-5</v>
@@ -560,7 +560,7 @@
         <v>Y</v>
       </c>
       <c r="J4" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="K4" t="str">
         <v>N</v>
@@ -586,7 +586,7 @@
         <v>Y</v>
       </c>
       <c r="D5" t="str">
-        <v>2025-04-15</v>
+        <v>2025-04-06</v>
       </c>
       <c r="E5" t="str">
         <v>Y</v>
@@ -595,7 +595,7 @@
         <v>Y</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H5" t="str">
         <v>1-5</v>
@@ -604,10 +604,10 @@
         <v>Y</v>
       </c>
       <c r="J5" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="K5" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="L5" t="str">
         <v>N</v>
@@ -630,16 +630,16 @@
         <v>Y</v>
       </c>
       <c r="D6" t="str">
-        <v>2025-04-02</v>
+        <v>2025-04-14</v>
       </c>
       <c r="E6" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F6" t="str">
         <v>Y</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" t="str">
         <v>1-5</v>
@@ -651,7 +651,7 @@
         <v>High</v>
       </c>
       <c r="K6" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L6" t="str">
         <v>N</v>
@@ -674,7 +674,7 @@
         <v>Y</v>
       </c>
       <c r="D7" t="str">
-        <v>2025-04-04</v>
+        <v>2025-04-08</v>
       </c>
       <c r="E7" t="str">
         <v>Y</v>
@@ -683,7 +683,7 @@
         <v>Y</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" t="str">
         <v>1-5</v>
@@ -692,7 +692,7 @@
         <v>Y</v>
       </c>
       <c r="J7" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K7" t="str">
         <v>N</v>
@@ -718,7 +718,7 @@
         <v>Y</v>
       </c>
       <c r="D8" t="str">
-        <v>2025-04-15</v>
+        <v>2025-04-13</v>
       </c>
       <c r="E8" t="str">
         <v>Y</v>
@@ -727,7 +727,7 @@
         <v>Y</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" t="str">
         <v>1-5</v>
@@ -736,7 +736,7 @@
         <v>Y</v>
       </c>
       <c r="J8" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="K8" t="str">
         <v>N</v>
@@ -762,7 +762,7 @@
         <v>Y</v>
       </c>
       <c r="D9" t="str">
-        <v>2025-04-13</v>
+        <v>2025-04-16</v>
       </c>
       <c r="E9" t="str">
         <v>Y</v>
@@ -771,7 +771,7 @@
         <v>Y</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H9" t="str">
         <v>1-5</v>
@@ -780,10 +780,10 @@
         <v>Y</v>
       </c>
       <c r="J9" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="K9" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L9" t="str">
         <v>N</v>
@@ -806,7 +806,7 @@
         <v>Y</v>
       </c>
       <c r="D10" t="str">
-        <v>2025-04-19</v>
+        <v>2025-04-15</v>
       </c>
       <c r="E10" t="str">
         <v>Y</v>
@@ -815,7 +815,7 @@
         <v>Y</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10" t="str">
         <v>1-5</v>
@@ -824,7 +824,7 @@
         <v>Y</v>
       </c>
       <c r="J10" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="K10" t="str">
         <v>N</v>
@@ -850,7 +850,7 @@
         <v>Y</v>
       </c>
       <c r="D11" t="str">
-        <v>2025-04-11</v>
+        <v>2025-04-03</v>
       </c>
       <c r="E11" t="str">
         <v>Y</v>
@@ -894,7 +894,7 @@
         <v>Y</v>
       </c>
       <c r="D12" t="str">
-        <v>2025-04-19</v>
+        <v>2025-04-20</v>
       </c>
       <c r="E12" t="str">
         <v>Y</v>
@@ -903,7 +903,7 @@
         <v>Y</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" t="str">
         <v>1-5</v>
@@ -912,7 +912,7 @@
         <v>Y</v>
       </c>
       <c r="J12" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="K12" t="str">
         <v>N</v>
@@ -938,7 +938,7 @@
         <v>Y</v>
       </c>
       <c r="D13" t="str">
-        <v>2025-04-01</v>
+        <v>2025-04-17</v>
       </c>
       <c r="E13" t="str">
         <v>Y</v>
@@ -947,7 +947,7 @@
         <v>Y</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H13" t="str">
         <v>1-5</v>
@@ -956,19 +956,19 @@
         <v>Y</v>
       </c>
       <c r="J13" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="K13" t="str">
         <v>N</v>
       </c>
       <c r="L13" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>2026-02-16</v>
       </c>
       <c r="N13" t="str">
-        <v/>
+        <v>Successful</v>
       </c>
     </row>
     <row r="14">
@@ -982,7 +982,7 @@
         <v>Y</v>
       </c>
       <c r="D14" t="str">
-        <v>2025-04-11</v>
+        <v>2025-04-18</v>
       </c>
       <c r="E14" t="str">
         <v>Y</v>
@@ -991,7 +991,7 @@
         <v>Y</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14" t="str">
         <v>1-5</v>
@@ -1000,7 +1000,7 @@
         <v>Y</v>
       </c>
       <c r="J14" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="K14" t="str">
         <v>N</v>
@@ -1026,7 +1026,7 @@
         <v>Y</v>
       </c>
       <c r="D15" t="str">
-        <v>2025-04-19</v>
+        <v>2025-04-04</v>
       </c>
       <c r="E15" t="str">
         <v>Y</v>
@@ -1035,7 +1035,7 @@
         <v>Y</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" t="str">
         <v>1-5</v>
@@ -1044,7 +1044,7 @@
         <v>Y</v>
       </c>
       <c r="J15" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="K15" t="str">
         <v>N</v>
@@ -1070,7 +1070,7 @@
         <v>Y</v>
       </c>
       <c r="D16" t="str">
-        <v>2025-04-17</v>
+        <v>2025-04-13</v>
       </c>
       <c r="E16" t="str">
         <v>Y</v>
@@ -1079,7 +1079,7 @@
         <v>Y</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16" t="str">
         <v>1-5</v>
@@ -1114,7 +1114,7 @@
         <v>Y</v>
       </c>
       <c r="D17" t="str">
-        <v>2025-04-13</v>
+        <v>2025-04-17</v>
       </c>
       <c r="E17" t="str">
         <v>Y</v>
@@ -1123,13 +1123,13 @@
         <v>Y</v>
       </c>
       <c r="G17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H17" t="str">
         <v>1-5</v>
       </c>
       <c r="I17" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J17" t="str">
         <v>Medium</v>
@@ -1158,7 +1158,7 @@
         <v>Y</v>
       </c>
       <c r="D18" t="str">
-        <v>2025-04-12</v>
+        <v>2025-04-18</v>
       </c>
       <c r="E18" t="str">
         <v>Y</v>
@@ -1167,7 +1167,7 @@
         <v>Y</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" t="str">
         <v>1-5</v>
@@ -1202,7 +1202,7 @@
         <v>Y</v>
       </c>
       <c r="D19" t="str">
-        <v>2025-04-02</v>
+        <v>2025-04-10</v>
       </c>
       <c r="E19" t="str">
         <v>Y</v>
@@ -1223,7 +1223,7 @@
         <v>Medium</v>
       </c>
       <c r="K19" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="L19" t="str">
         <v>N</v>
@@ -1246,7 +1246,7 @@
         <v>Y</v>
       </c>
       <c r="D20" t="str">
-        <v>2025-04-18</v>
+        <v>2025-04-12</v>
       </c>
       <c r="E20" t="str">
         <v>Y</v>
@@ -1290,7 +1290,7 @@
         <v>Y</v>
       </c>
       <c r="D21" t="str">
-        <v>2025-04-18</v>
+        <v>2025-04-17</v>
       </c>
       <c r="E21" t="str">
         <v>Y</v>
@@ -1311,7 +1311,7 @@
         <v>Low</v>
       </c>
       <c r="K21" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L21" t="str">
         <v>N</v>
@@ -1334,7 +1334,7 @@
         <v>Y</v>
       </c>
       <c r="D22" t="str">
-        <v>2025-04-08</v>
+        <v>2025-04-07</v>
       </c>
       <c r="E22" t="str">
         <v>Y</v>
@@ -1352,10 +1352,10 @@
         <v>Y</v>
       </c>
       <c r="J22" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K22" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L22" t="str">
         <v>N</v>
@@ -1378,7 +1378,7 @@
         <v>Y</v>
       </c>
       <c r="D23" t="str">
-        <v>2025-04-18</v>
+        <v>2025-04-16</v>
       </c>
       <c r="E23" t="str">
         <v>Y</v>
@@ -1387,19 +1387,19 @@
         <v>Y</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" t="str">
         <v>1-5</v>
       </c>
       <c r="I23" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="J23" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="K23" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L23" t="str">
         <v>N</v>
@@ -1422,7 +1422,7 @@
         <v>Y</v>
       </c>
       <c r="D24" t="str">
-        <v>2025-04-15</v>
+        <v>2025-04-10</v>
       </c>
       <c r="E24" t="str">
         <v>Y</v>
@@ -1443,7 +1443,7 @@
         <v>High</v>
       </c>
       <c r="K24" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L24" t="str">
         <v>N</v>
@@ -1466,7 +1466,7 @@
         <v>Y</v>
       </c>
       <c r="D25" t="str">
-        <v>2025-04-08</v>
+        <v>2025-04-05</v>
       </c>
       <c r="E25" t="str">
         <v>Y</v>
@@ -1484,7 +1484,7 @@
         <v>Y</v>
       </c>
       <c r="J25" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="K25" t="str">
         <v>N</v>
@@ -1510,10 +1510,10 @@
         <v>Y</v>
       </c>
       <c r="D26" t="str">
-        <v>2025-04-04</v>
+        <v>2025-04-06</v>
       </c>
       <c r="E26" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F26" t="str">
         <v>Y</v>
@@ -1554,10 +1554,10 @@
         <v>Y</v>
       </c>
       <c r="D27" t="str">
-        <v>2025-04-10</v>
+        <v>2025-04-03</v>
       </c>
       <c r="E27" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F27" t="str">
         <v>Y</v>
@@ -1575,7 +1575,7 @@
         <v>High</v>
       </c>
       <c r="K27" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="L27" t="str">
         <v>N</v>
@@ -1598,7 +1598,7 @@
         <v>Y</v>
       </c>
       <c r="D28" t="str">
-        <v>2025-04-05</v>
+        <v>2025-04-06</v>
       </c>
       <c r="E28" t="str">
         <v>Y</v>
@@ -1616,7 +1616,7 @@
         <v>Y</v>
       </c>
       <c r="J28" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="K28" t="str">
         <v>N</v>
@@ -1642,7 +1642,7 @@
         <v>Y</v>
       </c>
       <c r="D29" t="str">
-        <v>2025-04-06</v>
+        <v>2025-04-10</v>
       </c>
       <c r="E29" t="str">
         <v>Y</v>
@@ -1651,7 +1651,7 @@
         <v>Y</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" t="str">
         <v>1-5</v>
@@ -1660,7 +1660,7 @@
         <v>Y</v>
       </c>
       <c r="J29" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="K29" t="str">
         <v>N</v>
@@ -1686,10 +1686,10 @@
         <v>Y</v>
       </c>
       <c r="D30" t="str">
-        <v>2025-04-03</v>
+        <v>2025-04-08</v>
       </c>
       <c r="E30" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F30" t="str">
         <v>Y</v>
@@ -1745,22 +1745,22 @@
         <v>1-5</v>
       </c>
       <c r="I31" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="J31" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="K31" t="str">
         <v>N</v>
       </c>
       <c r="L31" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="M31" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="N31" t="str">
-        <v/>
+        <v>Open</v>
       </c>
     </row>
     <row r="32">
@@ -1774,7 +1774,7 @@
         <v>Y</v>
       </c>
       <c r="D32" t="str">
-        <v>2025-04-10</v>
+        <v>2025-04-20</v>
       </c>
       <c r="E32" t="str">
         <v>Y</v>
@@ -1789,7 +1789,7 @@
         <v>1-5</v>
       </c>
       <c r="I32" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="J32" t="str">
         <v>Low</v>
@@ -1818,7 +1818,7 @@
         <v>Y</v>
       </c>
       <c r="D33" t="str">
-        <v>2025-04-08</v>
+        <v>2025-04-06</v>
       </c>
       <c r="E33" t="str">
         <v>Y</v>
@@ -1839,7 +1839,7 @@
         <v>Low</v>
       </c>
       <c r="K33" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="L33" t="str">
         <v>N</v>
@@ -1871,7 +1871,7 @@
         <v>Y</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H34" t="str">
         <v>1-5</v>
@@ -1883,7 +1883,7 @@
         <v>Low</v>
       </c>
       <c r="K34" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L34" t="str">
         <v>N</v>
@@ -1906,25 +1906,25 @@
         <v>Y</v>
       </c>
       <c r="D35" t="str">
-        <v>2025-04-09</v>
+        <v>2025-04-14</v>
       </c>
       <c r="E35" t="str">
         <v>Y</v>
       </c>
       <c r="F35" t="str">
-        <v>N</v>
-      </c>
-      <c r="G35" t="str">
-        <v/>
+        <v>Y</v>
+      </c>
+      <c r="G35">
+        <v>4</v>
       </c>
       <c r="H35" t="str">
         <v>1-5</v>
       </c>
       <c r="I35" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J35" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="K35" t="str">
         <v>Y</v>
@@ -1950,28 +1950,28 @@
         <v>Y</v>
       </c>
       <c r="D36" t="str">
-        <v>2025-04-17</v>
+        <v>2025-04-19</v>
       </c>
       <c r="E36" t="str">
         <v>Y</v>
       </c>
       <c r="F36" t="str">
-        <v>N</v>
-      </c>
-      <c r="G36" t="str">
-        <v/>
+        <v>Y</v>
+      </c>
+      <c r="G36">
+        <v>4</v>
       </c>
       <c r="H36" t="str">
         <v>1-5</v>
       </c>
       <c r="I36" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J36" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K36" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L36" t="str">
         <v>N</v>
@@ -1994,28 +1994,28 @@
         <v>Y</v>
       </c>
       <c r="D37" t="str">
-        <v>2025-04-10</v>
+        <v>2025-04-03</v>
       </c>
       <c r="E37" t="str">
         <v>Y</v>
       </c>
       <c r="F37" t="str">
-        <v>N</v>
-      </c>
-      <c r="G37" t="str">
-        <v/>
+        <v>Y</v>
+      </c>
+      <c r="G37">
+        <v>5</v>
       </c>
       <c r="H37" t="str">
         <v>1-5</v>
       </c>
       <c r="I37" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J37" t="str">
         <v>Medium</v>
       </c>
       <c r="K37" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="L37" t="str">
         <v>N</v>
@@ -2038,7 +2038,7 @@
         <v>Y</v>
       </c>
       <c r="D38" t="str">
-        <v>2025-04-12</v>
+        <v>2025-04-04</v>
       </c>
       <c r="E38" t="str">
         <v>Y</v>
@@ -2056,19 +2056,19 @@
         <v>N</v>
       </c>
       <c r="J38" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="K38" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="L38" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="M38" t="str">
-        <v>2026-02-15</v>
+        <v/>
       </c>
       <c r="N38" t="str">
-        <v>Exited</v>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -2082,37 +2082,37 @@
         <v>Y</v>
       </c>
       <c r="D39" t="str">
-        <v>2025-04-20</v>
+        <v>2025-04-18</v>
       </c>
       <c r="E39" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F39" t="str">
-        <v>N</v>
-      </c>
-      <c r="G39" t="str">
-        <v/>
+        <v>Y</v>
+      </c>
+      <c r="G39">
+        <v>4</v>
       </c>
       <c r="H39" t="str">
         <v>1-5</v>
       </c>
       <c r="I39" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J39" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="K39" t="str">
         <v>N</v>
       </c>
       <c r="L39" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="M39" t="str">
-        <v>2026-01-27</v>
+        <v/>
       </c>
       <c r="N39" t="str">
-        <v>Open</v>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -2126,7 +2126,7 @@
         <v>Y</v>
       </c>
       <c r="D40" t="str">
-        <v>2025-04-04</v>
+        <v>2025-04-20</v>
       </c>
       <c r="E40" t="str">
         <v>Y</v>
@@ -2170,25 +2170,25 @@
         <v>Y</v>
       </c>
       <c r="D41" t="str">
-        <v>2025-04-15</v>
+        <v>2025-04-01</v>
       </c>
       <c r="E41" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F41" t="str">
-        <v>Y</v>
-      </c>
-      <c r="G41">
-        <v>4</v>
+        <v>N</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
       </c>
       <c r="H41" t="str">
         <v>1-5</v>
       </c>
       <c r="I41" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="J41" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="K41" t="str">
         <v>N</v>
@@ -2214,7 +2214,7 @@
         <v>Y</v>
       </c>
       <c r="D42" t="str">
-        <v>2025-04-15</v>
+        <v>2025-04-17</v>
       </c>
       <c r="E42" t="str">
         <v>Y</v>
@@ -2235,7 +2235,7 @@
         <v>Medium</v>
       </c>
       <c r="K42" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L42" t="str">
         <v>N</v>
@@ -2258,7 +2258,7 @@
         <v>Y</v>
       </c>
       <c r="D43" t="str">
-        <v>2025-04-11</v>
+        <v>2025-04-16</v>
       </c>
       <c r="E43" t="str">
         <v>Y</v>
@@ -2276,7 +2276,7 @@
         <v>N</v>
       </c>
       <c r="J43" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="K43" t="str">
         <v>N</v>
@@ -2302,22 +2302,22 @@
         <v>Y</v>
       </c>
       <c r="D44" t="str">
-        <v>2025-04-17</v>
+        <v>2025-04-14</v>
       </c>
       <c r="E44" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F44" t="str">
-        <v>N</v>
-      </c>
-      <c r="G44" t="str">
-        <v/>
+        <v>Y</v>
+      </c>
+      <c r="G44">
+        <v>4</v>
       </c>
       <c r="H44" t="str">
         <v>1-5</v>
       </c>
       <c r="I44" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J44" t="str">
         <v>Low</v>
@@ -2346,28 +2346,28 @@
         <v>Y</v>
       </c>
       <c r="D45" t="str">
-        <v>2025-04-01</v>
+        <v>2025-04-20</v>
       </c>
       <c r="E45" t="str">
         <v>Y</v>
       </c>
       <c r="F45" t="str">
-        <v>N</v>
-      </c>
-      <c r="G45" t="str">
-        <v/>
+        <v>Y</v>
+      </c>
+      <c r="G45">
+        <v>4</v>
       </c>
       <c r="H45" t="str">
         <v>1-5</v>
       </c>
       <c r="I45" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J45" t="str">
         <v>Low</v>
       </c>
       <c r="K45" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L45" t="str">
         <v>N</v>
@@ -2390,7 +2390,7 @@
         <v>Y</v>
       </c>
       <c r="D46" t="str">
-        <v>2025-04-02</v>
+        <v>2025-04-16</v>
       </c>
       <c r="E46" t="str">
         <v>Y</v>
@@ -2408,10 +2408,10 @@
         <v>N</v>
       </c>
       <c r="J46" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="K46" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="L46" t="str">
         <v>N</v>
@@ -2440,16 +2440,16 @@
         <v>Y</v>
       </c>
       <c r="F47" t="str">
-        <v>N</v>
-      </c>
-      <c r="G47" t="str">
-        <v/>
+        <v>Y</v>
+      </c>
+      <c r="G47">
+        <v>4</v>
       </c>
       <c r="H47" t="str">
         <v>1-5</v>
       </c>
       <c r="I47" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J47" t="str">
         <v>Low</v>
@@ -2478,7 +2478,7 @@
         <v>Y</v>
       </c>
       <c r="D48" t="str">
-        <v>2025-04-20</v>
+        <v>2025-04-07</v>
       </c>
       <c r="E48" t="str">
         <v>Y</v>
@@ -2528,22 +2528,22 @@
         <v>Y</v>
       </c>
       <c r="F49" t="str">
-        <v>N</v>
-      </c>
-      <c r="G49" t="str">
-        <v/>
+        <v>Y</v>
+      </c>
+      <c r="G49">
+        <v>3</v>
       </c>
       <c r="H49" t="str">
         <v>1-5</v>
       </c>
       <c r="I49" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J49" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="K49" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="L49" t="str">
         <v>N</v>
@@ -2566,7 +2566,7 @@
         <v>Y</v>
       </c>
       <c r="D50" t="str">
-        <v>2025-04-16</v>
+        <v>2025-04-04</v>
       </c>
       <c r="E50" t="str">
         <v>Y</v>
@@ -2610,7 +2610,7 @@
         <v>Y</v>
       </c>
       <c r="D51" t="str">
-        <v>2025-04-06</v>
+        <v>2025-04-13</v>
       </c>
       <c r="E51" t="str">
         <v>Y</v>
@@ -2628,7 +2628,7 @@
         <v>Y</v>
       </c>
       <c r="J51" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="K51" t="str">
         <v>N</v>
@@ -2654,16 +2654,16 @@
         <v>Y</v>
       </c>
       <c r="D52" t="str">
-        <v>2025-04-07</v>
+        <v>2025-04-20</v>
       </c>
       <c r="E52" t="str">
         <v>Y</v>
       </c>
       <c r="F52" t="str">
-        <v>N</v>
-      </c>
-      <c r="G52" t="str">
-        <v/>
+        <v>Y</v>
+      </c>
+      <c r="G52">
+        <v>3</v>
       </c>
       <c r="H52" t="str">
         <v>1-5</v>
@@ -2672,7 +2672,7 @@
         <v>N</v>
       </c>
       <c r="J52" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="K52" t="str">
         <v>N</v>
@@ -2698,25 +2698,25 @@
         <v>Y</v>
       </c>
       <c r="D53" t="str">
-        <v>2025-04-11</v>
+        <v>2025-04-19</v>
       </c>
       <c r="E53" t="str">
         <v>Y</v>
       </c>
       <c r="F53" t="str">
-        <v>Y</v>
-      </c>
-      <c r="G53">
-        <v>3</v>
+        <v>N</v>
+      </c>
+      <c r="G53" t="str">
+        <v/>
       </c>
       <c r="H53" t="str">
         <v>1-5</v>
       </c>
       <c r="I53" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="J53" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K53" t="str">
         <v>N</v>
@@ -2742,25 +2742,25 @@
         <v>Y</v>
       </c>
       <c r="D54" t="str">
-        <v>2025-04-04</v>
+        <v>2025-04-02</v>
       </c>
       <c r="E54" t="str">
         <v>Y</v>
       </c>
       <c r="F54" t="str">
-        <v>N</v>
-      </c>
-      <c r="G54" t="str">
-        <v/>
+        <v>Y</v>
+      </c>
+      <c r="G54">
+        <v>3</v>
       </c>
       <c r="H54" t="str">
         <v>1-5</v>
       </c>
       <c r="I54" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J54" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K54" t="str">
         <v>N</v>
@@ -2786,7 +2786,7 @@
         <v>Y</v>
       </c>
       <c r="D55" t="str">
-        <v>2025-04-13</v>
+        <v>2025-04-09</v>
       </c>
       <c r="E55" t="str">
         <v>Y</v>
@@ -2795,16 +2795,16 @@
         <v>Y</v>
       </c>
       <c r="G55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H55" t="str">
         <v>1-5</v>
       </c>
       <c r="I55" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="J55" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="K55" t="str">
         <v>N</v>
@@ -2830,7 +2830,7 @@
         <v>Y</v>
       </c>
       <c r="D56" t="str">
-        <v>2025-04-20</v>
+        <v>2025-04-18</v>
       </c>
       <c r="E56" t="str">
         <v>Y</v>
@@ -2839,16 +2839,16 @@
         <v>Y</v>
       </c>
       <c r="G56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H56" t="str">
         <v>1-5</v>
       </c>
       <c r="I56" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J56" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="K56" t="str">
         <v>N</v>
@@ -2874,7 +2874,7 @@
         <v>Y</v>
       </c>
       <c r="D57" t="str">
-        <v>2025-04-19</v>
+        <v>2025-04-15</v>
       </c>
       <c r="E57" t="str">
         <v>Y</v>
@@ -2892,7 +2892,7 @@
         <v>N</v>
       </c>
       <c r="J57" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="K57" t="str">
         <v>N</v>
@@ -2918,7 +2918,7 @@
         <v>Y</v>
       </c>
       <c r="D58" t="str">
-        <v>2025-04-02</v>
+        <v>2025-04-04</v>
       </c>
       <c r="E58" t="str">
         <v>Y</v>
@@ -2927,7 +2927,7 @@
         <v>Y</v>
       </c>
       <c r="G58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H58" t="str">
         <v>1-5</v>
@@ -2936,19 +2936,19 @@
         <v>Y</v>
       </c>
       <c r="J58" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="K58" t="str">
         <v>N</v>
       </c>
       <c r="L58" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="M58" t="str">
-        <v/>
+        <v>2026-01-02</v>
       </c>
       <c r="N58" t="str">
-        <v/>
+        <v>Open</v>
       </c>
     </row>
     <row r="59">
@@ -2962,7 +2962,7 @@
         <v>Y</v>
       </c>
       <c r="D59" t="str">
-        <v>2025-04-09</v>
+        <v>2025-04-03</v>
       </c>
       <c r="E59" t="str">
         <v>Y</v>
@@ -2971,19 +2971,19 @@
         <v>Y</v>
       </c>
       <c r="G59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H59" t="str">
         <v>1-5</v>
       </c>
       <c r="I59" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J59" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="K59" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L59" t="str">
         <v>N</v>
@@ -3006,7 +3006,7 @@
         <v>Y</v>
       </c>
       <c r="D60" t="str">
-        <v>2025-04-18</v>
+        <v>2025-04-20</v>
       </c>
       <c r="E60" t="str">
         <v>Y</v>
@@ -3015,7 +3015,7 @@
         <v>Y</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H60" t="str">
         <v>1-5</v>
@@ -3027,7 +3027,7 @@
         <v>Medium</v>
       </c>
       <c r="K60" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L60" t="str">
         <v>N</v>
@@ -3050,7 +3050,7 @@
         <v>Y</v>
       </c>
       <c r="D61" t="str">
-        <v>2025-04-15</v>
+        <v>2025-04-17</v>
       </c>
       <c r="E61" t="str">
         <v>Y</v>
@@ -3059,7 +3059,7 @@
         <v>Y</v>
       </c>
       <c r="G61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H61" t="str">
         <v>1-5</v>
@@ -3068,7 +3068,7 @@
         <v>Y</v>
       </c>
       <c r="J61" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="K61" t="str">
         <v>N</v>
@@ -3094,25 +3094,25 @@
         <v>Y</v>
       </c>
       <c r="D62" t="str">
-        <v>2025-04-01</v>
+        <v>2025-04-06</v>
       </c>
       <c r="E62" t="str">
         <v>Y</v>
       </c>
       <c r="F62" t="str">
-        <v>Y</v>
-      </c>
-      <c r="G62">
-        <v>2</v>
+        <v>N</v>
+      </c>
+      <c r="G62" t="str">
+        <v/>
       </c>
       <c r="H62" t="str">
         <v>1-5</v>
       </c>
       <c r="I62" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="J62" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="K62" t="str">
         <v>N</v>
@@ -3138,7 +3138,7 @@
         <v>Y</v>
       </c>
       <c r="D63" t="str">
-        <v>2025-04-16</v>
+        <v>2025-04-01</v>
       </c>
       <c r="E63" t="str">
         <v>Y</v>
@@ -3156,7 +3156,7 @@
         <v>Y</v>
       </c>
       <c r="J63" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="K63" t="str">
         <v>N</v>
@@ -3182,10 +3182,10 @@
         <v>Y</v>
       </c>
       <c r="D64" t="str">
-        <v>2025-04-07</v>
+        <v>2025-04-06</v>
       </c>
       <c r="E64" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F64" t="str">
         <v>Y</v>
@@ -3200,19 +3200,19 @@
         <v>Y</v>
       </c>
       <c r="J64" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="K64" t="str">
         <v>N</v>
       </c>
       <c r="L64" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="M64" t="str">
-        <v/>
+        <v>2026-03-02</v>
       </c>
       <c r="N64" t="str">
-        <v/>
+        <v>Exited</v>
       </c>
     </row>
     <row r="65">
@@ -3226,7 +3226,7 @@
         <v>Y</v>
       </c>
       <c r="D65" t="str">
-        <v>2025-04-04</v>
+        <v>2025-04-17</v>
       </c>
       <c r="E65" t="str">
         <v>Y</v>
@@ -3244,7 +3244,7 @@
         <v>N</v>
       </c>
       <c r="J65" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="K65" t="str">
         <v>N</v>
@@ -3270,25 +3270,25 @@
         <v>Y</v>
       </c>
       <c r="D66" t="str">
-        <v>2025-04-10</v>
+        <v>2025-04-04</v>
       </c>
       <c r="E66" t="str">
         <v>Y</v>
       </c>
       <c r="F66" t="str">
-        <v>Y</v>
-      </c>
-      <c r="G66">
-        <v>4</v>
+        <v>N</v>
+      </c>
+      <c r="G66" t="str">
+        <v/>
       </c>
       <c r="H66" t="str">
         <v>1-5</v>
       </c>
       <c r="I66" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="J66" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="K66" t="str">
         <v>N</v>
@@ -3314,7 +3314,7 @@
         <v>Y</v>
       </c>
       <c r="D67" t="str">
-        <v>2025-04-01</v>
+        <v>2025-04-04</v>
       </c>
       <c r="E67" t="str">
         <v>Y</v>
@@ -3323,7 +3323,7 @@
         <v>Y</v>
       </c>
       <c r="G67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H67" t="str">
         <v>1-5</v>
@@ -3332,7 +3332,7 @@
         <v>Y</v>
       </c>
       <c r="J67" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="K67" t="str">
         <v>N</v>
@@ -3358,7 +3358,7 @@
         <v>Y</v>
       </c>
       <c r="D68" t="str">
-        <v>2025-04-06</v>
+        <v>2025-04-02</v>
       </c>
       <c r="E68" t="str">
         <v>Y</v>
@@ -3367,7 +3367,7 @@
         <v>Y</v>
       </c>
       <c r="G68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H68" t="str">
         <v>1-5</v>
@@ -3376,19 +3376,19 @@
         <v>Y</v>
       </c>
       <c r="J68" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="K68" t="str">
         <v>N</v>
       </c>
       <c r="L68" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="M68" t="str">
-        <v>2026-03-02</v>
+        <v/>
       </c>
       <c r="N68" t="str">
-        <v>Exited</v>
+        <v/>
       </c>
     </row>
     <row r="69">
@@ -3402,7 +3402,7 @@
         <v>Y</v>
       </c>
       <c r="D69" t="str">
-        <v>2025-04-17</v>
+        <v>2025-04-19</v>
       </c>
       <c r="E69" t="str">
         <v>Y</v>
@@ -3411,19 +3411,19 @@
         <v>Y</v>
       </c>
       <c r="G69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H69" t="str">
         <v>1-5</v>
       </c>
       <c r="I69" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J69" t="str">
         <v>Medium</v>
       </c>
       <c r="K69" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L69" t="str">
         <v>N</v>
@@ -3446,16 +3446,16 @@
         <v>Y</v>
       </c>
       <c r="D70" t="str">
-        <v>2025-04-04</v>
+        <v>2025-04-19</v>
       </c>
       <c r="E70" t="str">
         <v>Y</v>
       </c>
       <c r="F70" t="str">
-        <v>N</v>
-      </c>
-      <c r="G70" t="str">
-        <v/>
+        <v>Y</v>
+      </c>
+      <c r="G70">
+        <v>4</v>
       </c>
       <c r="H70" t="str">
         <v>1-5</v>
@@ -3464,7 +3464,7 @@
         <v>N</v>
       </c>
       <c r="J70" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="K70" t="str">
         <v>N</v>
@@ -3499,7 +3499,7 @@
         <v>Y</v>
       </c>
       <c r="G71">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H71" t="str">
         <v>1-5</v>
@@ -3508,10 +3508,10 @@
         <v>Y</v>
       </c>
       <c r="J71" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K71" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L71" t="str">
         <v>N</v>
@@ -3534,7 +3534,7 @@
         <v>Y</v>
       </c>
       <c r="D72" t="str">
-        <v>2025-04-02</v>
+        <v>2025-04-08</v>
       </c>
       <c r="E72" t="str">
         <v>Y</v>
@@ -3578,10 +3578,10 @@
         <v>Y</v>
       </c>
       <c r="D73" t="str">
-        <v>2025-04-19</v>
+        <v>2025-04-11</v>
       </c>
       <c r="E73" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F73" t="str">
         <v>Y</v>
@@ -3599,7 +3599,7 @@
         <v>Medium</v>
       </c>
       <c r="K73" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="L73" t="str">
         <v>N</v>
@@ -3622,25 +3622,25 @@
         <v>Y</v>
       </c>
       <c r="D74" t="str">
-        <v>2025-04-19</v>
+        <v>2025-04-03</v>
       </c>
       <c r="E74" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F74" t="str">
         <v>Y</v>
       </c>
       <c r="G74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H74" t="str">
         <v>1-5</v>
       </c>
       <c r="I74" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J74" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="K74" t="str">
         <v>N</v>
@@ -3666,16 +3666,16 @@
         <v>Y</v>
       </c>
       <c r="D75" t="str">
-        <v>2025-04-04</v>
+        <v>2025-04-11</v>
       </c>
       <c r="E75" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F75" t="str">
         <v>Y</v>
       </c>
       <c r="G75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H75" t="str">
         <v>1-5</v>
@@ -3684,10 +3684,10 @@
         <v>Y</v>
       </c>
       <c r="J75" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="K75" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="L75" t="str">
         <v>N</v>
@@ -3710,7 +3710,7 @@
         <v>Y</v>
       </c>
       <c r="D76" t="str">
-        <v>2025-04-08</v>
+        <v>2025-04-19</v>
       </c>
       <c r="E76" t="str">
         <v>Y</v>
@@ -3728,7 +3728,7 @@
         <v>Y</v>
       </c>
       <c r="J76" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="K76" t="str">
         <v>N</v>
@@ -3754,16 +3754,16 @@
         <v>Y</v>
       </c>
       <c r="D77" t="str">
-        <v>2025-04-11</v>
+        <v>2025-04-15</v>
       </c>
       <c r="E77" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F77" t="str">
         <v>Y</v>
       </c>
       <c r="G77">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H77" t="str">
         <v>1-5</v>
@@ -3798,16 +3798,16 @@
         <v>Y</v>
       </c>
       <c r="D78" t="str">
-        <v>2025-04-03</v>
+        <v>2025-04-11</v>
       </c>
       <c r="E78" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F78" t="str">
         <v>Y</v>
       </c>
       <c r="G78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H78" t="str">
         <v>1-5</v>
@@ -3822,13 +3822,13 @@
         <v>N</v>
       </c>
       <c r="L78" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="M78" t="str">
-        <v/>
+        <v>2026-03-09</v>
       </c>
       <c r="N78" t="str">
-        <v/>
+        <v>Open</v>
       </c>
     </row>
     <row r="79">
@@ -3842,10 +3842,10 @@
         <v>Y</v>
       </c>
       <c r="D79" t="str">
-        <v>2025-04-11</v>
+        <v>2025-04-08</v>
       </c>
       <c r="E79" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F79" t="str">
         <v>Y</v>
@@ -3886,7 +3886,7 @@
         <v>Y</v>
       </c>
       <c r="D80" t="str">
-        <v>2025-04-19</v>
+        <v>2025-04-20</v>
       </c>
       <c r="E80" t="str">
         <v>Y</v>
@@ -3895,7 +3895,7 @@
         <v>Y</v>
       </c>
       <c r="G80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H80" t="str">
         <v>1-5</v>
@@ -3930,7 +3930,7 @@
         <v>Y</v>
       </c>
       <c r="D81" t="str">
-        <v>2025-04-15</v>
+        <v>2025-04-08</v>
       </c>
       <c r="E81" t="str">
         <v>Y</v>
@@ -3939,7 +3939,7 @@
         <v>Y</v>
       </c>
       <c r="G81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H81" t="str">
         <v>1-5</v>
@@ -3974,7 +3974,7 @@
         <v>Y</v>
       </c>
       <c r="D82" t="str">
-        <v>2025-04-11</v>
+        <v>2025-04-02</v>
       </c>
       <c r="E82" t="str">
         <v>Y</v>
@@ -3983,7 +3983,7 @@
         <v>Y</v>
       </c>
       <c r="G82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H82" t="str">
         <v>1-5</v>
@@ -3992,19 +3992,19 @@
         <v>Y</v>
       </c>
       <c r="J82" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K82" t="str">
         <v>N</v>
       </c>
       <c r="L82" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="M82" t="str">
-        <v>2026-03-09</v>
+        <v/>
       </c>
       <c r="N82" t="str">
-        <v>Open</v>
+        <v/>
       </c>
     </row>
     <row r="83">
@@ -4018,10 +4018,10 @@
         <v>Y</v>
       </c>
       <c r="D83" t="str">
-        <v>2025-04-08</v>
+        <v>2025-04-07</v>
       </c>
       <c r="E83" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F83" t="str">
         <v>N</v>
@@ -4036,7 +4036,7 @@
         <v>N</v>
       </c>
       <c r="J83" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="K83" t="str">
         <v>N</v>
@@ -4062,37 +4062,37 @@
         <v>Y</v>
       </c>
       <c r="D84" t="str">
-        <v>2025-04-19</v>
+        <v>2025-04-11</v>
       </c>
       <c r="E84" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F84" t="str">
-        <v>N</v>
-      </c>
-      <c r="G84" t="str">
-        <v/>
+        <v>Y</v>
+      </c>
+      <c r="G84">
+        <v>3</v>
       </c>
       <c r="H84" t="str">
         <v>1-5</v>
       </c>
       <c r="I84" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J84" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="K84" t="str">
         <v>N</v>
       </c>
       <c r="L84" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="M84" t="str">
-        <v>2026-02-19</v>
+        <v/>
       </c>
       <c r="N84" t="str">
-        <v>Open</v>
+        <v/>
       </c>
     </row>
     <row r="85">
@@ -4106,22 +4106,22 @@
         <v>Y</v>
       </c>
       <c r="D85" t="str">
-        <v>2025-04-14</v>
+        <v>2025-04-04</v>
       </c>
       <c r="E85" t="str">
         <v>Y</v>
       </c>
       <c r="F85" t="str">
-        <v>Y</v>
-      </c>
-      <c r="G85">
-        <v>3</v>
+        <v>N</v>
+      </c>
+      <c r="G85" t="str">
+        <v/>
       </c>
       <c r="H85" t="str">
         <v>1-5</v>
       </c>
       <c r="I85" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="J85" t="str">
         <v>Low</v>
@@ -4150,22 +4150,22 @@
         <v>Y</v>
       </c>
       <c r="D86" t="str">
-        <v>2025-04-04</v>
+        <v>2025-04-20</v>
       </c>
       <c r="E86" t="str">
         <v>Y</v>
       </c>
       <c r="F86" t="str">
-        <v>N</v>
-      </c>
-      <c r="G86" t="str">
-        <v/>
+        <v>Y</v>
+      </c>
+      <c r="G86">
+        <v>3</v>
       </c>
       <c r="H86" t="str">
         <v>1-5</v>
       </c>
       <c r="I86" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J86" t="str">
         <v>Medium</v>
@@ -4194,10 +4194,10 @@
         <v>Y</v>
       </c>
       <c r="D87" t="str">
-        <v>2025-04-07</v>
+        <v>2025-04-06</v>
       </c>
       <c r="E87" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F87" t="str">
         <v>N</v>
@@ -4238,22 +4238,22 @@
         <v>Y</v>
       </c>
       <c r="D88" t="str">
-        <v>2025-04-11</v>
+        <v>2025-04-14</v>
       </c>
       <c r="E88" t="str">
         <v>Y</v>
       </c>
       <c r="F88" t="str">
-        <v>Y</v>
-      </c>
-      <c r="G88">
-        <v>3</v>
+        <v>N</v>
+      </c>
+      <c r="G88" t="str">
+        <v/>
       </c>
       <c r="H88" t="str">
         <v>1-5</v>
       </c>
       <c r="I88" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="J88" t="str">
         <v>Medium</v>
@@ -4282,7 +4282,7 @@
         <v>Y</v>
       </c>
       <c r="D89" t="str">
-        <v>2025-04-04</v>
+        <v>2025-04-10</v>
       </c>
       <c r="E89" t="str">
         <v>Y</v>
@@ -4300,10 +4300,10 @@
         <v>N</v>
       </c>
       <c r="J89" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="K89" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L89" t="str">
         <v>N</v>
@@ -4326,7 +4326,7 @@
         <v>Y</v>
       </c>
       <c r="D90" t="str">
-        <v>2025-04-20</v>
+        <v>2025-04-07</v>
       </c>
       <c r="E90" t="str">
         <v>Y</v>
@@ -4335,7 +4335,7 @@
         <v>Y</v>
       </c>
       <c r="G90">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H90" t="str">
         <v>1-5</v>
@@ -4350,13 +4350,13 @@
         <v>N</v>
       </c>
       <c r="L90" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="M90" t="str">
-        <v/>
+        <v>2026-01-24</v>
       </c>
       <c r="N90" t="str">
-        <v/>
+        <v>Open</v>
       </c>
     </row>
     <row r="91">
@@ -4370,10 +4370,10 @@
         <v>Y</v>
       </c>
       <c r="D91" t="str">
-        <v>2025-04-06</v>
+        <v>2025-04-09</v>
       </c>
       <c r="E91" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F91" t="str">
         <v>N</v>
@@ -4388,7 +4388,7 @@
         <v>N</v>
       </c>
       <c r="J91" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="K91" t="str">
         <v>N</v>
@@ -4414,7 +4414,7 @@
         <v>Y</v>
       </c>
       <c r="D92" t="str">
-        <v>2025-04-14</v>
+        <v>2025-04-10</v>
       </c>
       <c r="E92" t="str">
         <v>Y</v>
@@ -4458,7 +4458,7 @@
         <v>Y</v>
       </c>
       <c r="D93" t="str">
-        <v>2025-04-10</v>
+        <v>2025-04-03</v>
       </c>
       <c r="E93" t="str">
         <v>Y</v>
@@ -4476,7 +4476,7 @@
         <v>N</v>
       </c>
       <c r="J93" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="K93" t="str">
         <v>Y</v>
@@ -4502,37 +4502,37 @@
         <v>Y</v>
       </c>
       <c r="D94" t="str">
-        <v>2025-04-07</v>
+        <v>2025-04-15</v>
       </c>
       <c r="E94" t="str">
         <v>Y</v>
       </c>
       <c r="F94" t="str">
-        <v>Y</v>
-      </c>
-      <c r="G94">
-        <v>4</v>
+        <v>N</v>
+      </c>
+      <c r="G94" t="str">
+        <v/>
       </c>
       <c r="H94" t="str">
         <v>1-5</v>
       </c>
       <c r="I94" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="J94" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="K94" t="str">
         <v>N</v>
       </c>
       <c r="L94" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="M94" t="str">
-        <v>2026-01-24</v>
+        <v/>
       </c>
       <c r="N94" t="str">
-        <v>Open</v>
+        <v/>
       </c>
     </row>
     <row r="95">
@@ -4546,28 +4546,28 @@
         <v>Y</v>
       </c>
       <c r="D95" t="str">
-        <v>2025-04-09</v>
+        <v>2025-04-15</v>
       </c>
       <c r="E95" t="str">
         <v>N</v>
       </c>
       <c r="F95" t="str">
-        <v>N</v>
-      </c>
-      <c r="G95" t="str">
-        <v/>
+        <v>Y</v>
+      </c>
+      <c r="G95">
+        <v>4</v>
       </c>
       <c r="H95" t="str">
         <v>1-5</v>
       </c>
       <c r="I95" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J95" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="K95" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L95" t="str">
         <v>N</v>
@@ -4590,7 +4590,7 @@
         <v>Y</v>
       </c>
       <c r="D96" t="str">
-        <v>2025-04-10</v>
+        <v>2025-04-03</v>
       </c>
       <c r="E96" t="str">
         <v>Y</v>
@@ -4608,7 +4608,7 @@
         <v>N</v>
       </c>
       <c r="J96" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="K96" t="str">
         <v>N</v>
@@ -4634,28 +4634,28 @@
         <v>Y</v>
       </c>
       <c r="D97" t="str">
-        <v>2025-04-03</v>
+        <v>2025-04-04</v>
       </c>
       <c r="E97" t="str">
         <v>Y</v>
       </c>
       <c r="F97" t="str">
-        <v>N</v>
-      </c>
-      <c r="G97" t="str">
-        <v/>
+        <v>Y</v>
+      </c>
+      <c r="G97">
+        <v>5</v>
       </c>
       <c r="H97" t="str">
         <v>1-5</v>
       </c>
       <c r="I97" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J97" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="K97" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="L97" t="str">
         <v>N</v>
@@ -4678,7 +4678,7 @@
         <v>Y</v>
       </c>
       <c r="D98" t="str">
-        <v>2025-04-15</v>
+        <v>2025-04-04</v>
       </c>
       <c r="E98" t="str">
         <v>Y</v>
@@ -4687,7 +4687,7 @@
         <v>Y</v>
       </c>
       <c r="G98">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H98" t="str">
         <v>1-5</v>
@@ -4722,25 +4722,25 @@
         <v>Y</v>
       </c>
       <c r="D99" t="str">
-        <v>2025-04-19</v>
+        <v>2025-04-04</v>
       </c>
       <c r="E99" t="str">
         <v>Y</v>
       </c>
       <c r="F99" t="str">
-        <v>Y</v>
-      </c>
-      <c r="G99">
-        <v>3</v>
+        <v>N</v>
+      </c>
+      <c r="G99" t="str">
+        <v/>
       </c>
       <c r="H99" t="str">
         <v>1-5</v>
       </c>
       <c r="I99" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="J99" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="K99" t="str">
         <v>N</v>
@@ -4766,7 +4766,7 @@
         <v>Y</v>
       </c>
       <c r="D100" t="str">
-        <v>2025-04-03</v>
+        <v>2025-04-04</v>
       </c>
       <c r="E100" t="str">
         <v>Y</v>
@@ -4775,7 +4775,7 @@
         <v>Y</v>
       </c>
       <c r="G100">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H100" t="str">
         <v>1-5</v>
@@ -4810,25 +4810,25 @@
         <v>Y</v>
       </c>
       <c r="D101" t="str">
-        <v>2025-04-19</v>
+        <v>2025-04-13</v>
       </c>
       <c r="E101" t="str">
         <v>Y</v>
       </c>
       <c r="F101" t="str">
-        <v>N</v>
-      </c>
-      <c r="G101" t="str">
-        <v/>
+        <v>Y</v>
+      </c>
+      <c r="G101">
+        <v>3</v>
       </c>
       <c r="H101" t="str">
         <v>1-5</v>
       </c>
       <c r="I101" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J101" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="K101" t="str">
         <v>N</v>
@@ -4854,7 +4854,7 @@
         <v>Y</v>
       </c>
       <c r="D102" t="str">
-        <v>2025-04-12</v>
+        <v>2025-04-11</v>
       </c>
       <c r="E102" t="str">
         <v>Y</v>
@@ -4863,7 +4863,7 @@
         <v>Y</v>
       </c>
       <c r="G102">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H102" t="str">
         <v>1-5</v>
@@ -4872,19 +4872,19 @@
         <v>Y</v>
       </c>
       <c r="J102" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="K102" t="str">
         <v>N</v>
       </c>
       <c r="L102" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="M102" t="str">
-        <v>2026-03-02</v>
+        <v/>
       </c>
       <c r="N102" t="str">
-        <v>Successful</v>
+        <v/>
       </c>
     </row>
     <row r="103">
@@ -4898,25 +4898,25 @@
         <v>Y</v>
       </c>
       <c r="D103" t="str">
-        <v>2025-04-08</v>
+        <v>2025-04-18</v>
       </c>
       <c r="E103" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F103" t="str">
-        <v>Y</v>
-      </c>
-      <c r="G103">
-        <v>3</v>
+        <v>N</v>
+      </c>
+      <c r="G103" t="str">
+        <v/>
       </c>
       <c r="H103" t="str">
         <v>1-5</v>
       </c>
       <c r="I103" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="J103" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="K103" t="str">
         <v>N</v>
@@ -4942,25 +4942,25 @@
         <v>Y</v>
       </c>
       <c r="D104" t="str">
-        <v>2025-04-20</v>
+        <v>2025-04-04</v>
       </c>
       <c r="E104" t="str">
         <v>Y</v>
       </c>
       <c r="F104" t="str">
-        <v>Y</v>
-      </c>
-      <c r="G104">
-        <v>4</v>
+        <v>N</v>
+      </c>
+      <c r="G104" t="str">
+        <v/>
       </c>
       <c r="H104" t="str">
         <v>1-5</v>
       </c>
       <c r="I104" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="J104" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K104" t="str">
         <v>N</v>
@@ -4992,16 +4992,16 @@
         <v>Y</v>
       </c>
       <c r="F105" t="str">
-        <v>Y</v>
-      </c>
-      <c r="G105">
-        <v>3</v>
+        <v>N</v>
+      </c>
+      <c r="G105" t="str">
+        <v/>
       </c>
       <c r="H105" t="str">
         <v>1-5</v>
       </c>
       <c r="I105" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="J105" t="str">
         <v>Medium</v>
@@ -5030,7 +5030,7 @@
         <v>Y</v>
       </c>
       <c r="D106" t="str">
-        <v>2025-04-19</v>
+        <v>2025-04-07</v>
       </c>
       <c r="E106" t="str">
         <v>Y</v>
@@ -5039,7 +5039,7 @@
         <v>Y</v>
       </c>
       <c r="G106">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H106" t="str">
         <v>1-5</v>
@@ -5048,10 +5048,10 @@
         <v>Y</v>
       </c>
       <c r="J106" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="K106" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="L106" t="str">
         <v>N</v>
@@ -5074,16 +5074,16 @@
         <v>Y</v>
       </c>
       <c r="D107" t="str">
-        <v>2025-04-09</v>
+        <v>2025-04-13</v>
       </c>
       <c r="E107" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F107" t="str">
         <v>Y</v>
       </c>
       <c r="G107">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H107" t="str">
         <v>1-5</v>
@@ -5092,7 +5092,7 @@
         <v>Y</v>
       </c>
       <c r="J107" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="K107" t="str">
         <v>N</v>
@@ -5118,25 +5118,25 @@
         <v>Y</v>
       </c>
       <c r="D108" t="str">
-        <v>2025-04-14</v>
+        <v>2025-04-06</v>
       </c>
       <c r="E108" t="str">
         <v>Y</v>
       </c>
       <c r="F108" t="str">
-        <v>N</v>
-      </c>
-      <c r="G108" t="str">
-        <v/>
+        <v>Y</v>
+      </c>
+      <c r="G108">
+        <v>4</v>
       </c>
       <c r="H108" t="str">
         <v>1-5</v>
       </c>
       <c r="I108" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J108" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K108" t="str">
         <v>N</v>
@@ -5162,7 +5162,7 @@
         <v>Y</v>
       </c>
       <c r="D109" t="str">
-        <v>2025-04-07</v>
+        <v>2025-04-04</v>
       </c>
       <c r="E109" t="str">
         <v>Y</v>
@@ -5180,7 +5180,7 @@
         <v>Y</v>
       </c>
       <c r="J109" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="K109" t="str">
         <v>N</v>
@@ -5209,7 +5209,7 @@
         <v>2025-04-13</v>
       </c>
       <c r="E110" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F110" t="str">
         <v>Y</v>
@@ -5250,7 +5250,7 @@
         <v>Y</v>
       </c>
       <c r="D111" t="str">
-        <v>2025-04-06</v>
+        <v>2025-04-15</v>
       </c>
       <c r="E111" t="str">
         <v>Y</v>
@@ -5268,7 +5268,7 @@
         <v>Y</v>
       </c>
       <c r="J111" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="K111" t="str">
         <v>N</v>
@@ -5294,7 +5294,7 @@
         <v>Y</v>
       </c>
       <c r="D112" t="str">
-        <v>2025-04-04</v>
+        <v>2025-04-03</v>
       </c>
       <c r="E112" t="str">
         <v>Y</v>
@@ -5303,7 +5303,7 @@
         <v>Y</v>
       </c>
       <c r="G112">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H112" t="str">
         <v>1-5</v>
@@ -5338,7 +5338,7 @@
         <v>Y</v>
       </c>
       <c r="D113" t="str">
-        <v>2025-04-13</v>
+        <v>2025-04-05</v>
       </c>
       <c r="E113" t="str">
         <v>Y</v>
@@ -5382,7 +5382,7 @@
         <v>Y</v>
       </c>
       <c r="D114" t="str">
-        <v>2025-04-15</v>
+        <v>2025-04-18</v>
       </c>
       <c r="E114" t="str">
         <v>Y</v>
@@ -5391,7 +5391,7 @@
         <v>Y</v>
       </c>
       <c r="G114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H114" t="str">
         <v>1-5</v>
@@ -5426,7 +5426,7 @@
         <v>Y</v>
       </c>
       <c r="D115" t="str">
-        <v>2025-04-03</v>
+        <v>2025-04-15</v>
       </c>
       <c r="E115" t="str">
         <v>Y</v>
@@ -5447,7 +5447,7 @@
         <v>Low</v>
       </c>
       <c r="K115" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L115" t="str">
         <v>N</v>
@@ -5470,7 +5470,7 @@
         <v>Y</v>
       </c>
       <c r="D116" t="str">
-        <v>2025-04-05</v>
+        <v>2025-04-03</v>
       </c>
       <c r="E116" t="str">
         <v>Y</v>
@@ -5514,7 +5514,7 @@
         <v>Y</v>
       </c>
       <c r="D117" t="str">
-        <v>2025-04-18</v>
+        <v>2025-04-16</v>
       </c>
       <c r="E117" t="str">
         <v>Y</v>
@@ -5532,7 +5532,7 @@
         <v>Y</v>
       </c>
       <c r="J117" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="K117" t="str">
         <v>N</v>
@@ -5558,7 +5558,7 @@
         <v>Y</v>
       </c>
       <c r="D118" t="str">
-        <v>2025-04-15</v>
+        <v>2025-04-12</v>
       </c>
       <c r="E118" t="str">
         <v>Y</v>
@@ -5567,7 +5567,7 @@
         <v>Y</v>
       </c>
       <c r="G118">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H118" t="str">
         <v>1-5</v>
@@ -5576,10 +5576,10 @@
         <v>Y</v>
       </c>
       <c r="J118" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="K118" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="L118" t="str">
         <v>N</v>
@@ -5611,7 +5611,7 @@
         <v>Y</v>
       </c>
       <c r="G119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H119" t="str">
         <v>1-5</v>
@@ -5646,7 +5646,7 @@
         <v>Y</v>
       </c>
       <c r="D120" t="str">
-        <v>2025-04-16</v>
+        <v>2025-04-03</v>
       </c>
       <c r="E120" t="str">
         <v>Y</v>
@@ -5655,7 +5655,7 @@
         <v>Y</v>
       </c>
       <c r="G120">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H120" t="str">
         <v>1-5</v>
@@ -5664,7 +5664,7 @@
         <v>Y</v>
       </c>
       <c r="J120" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="K120" t="str">
         <v>N</v>
@@ -5690,28 +5690,28 @@
         <v>Y</v>
       </c>
       <c r="D121" t="str">
-        <v>2025-04-12</v>
+        <v>2025-04-13</v>
       </c>
       <c r="E121" t="str">
         <v>Y</v>
       </c>
       <c r="F121" t="str">
-        <v>Y</v>
-      </c>
-      <c r="G121">
-        <v>3</v>
+        <v>N</v>
+      </c>
+      <c r="G121" t="str">
+        <v/>
       </c>
       <c r="H121" t="str">
         <v>1-5</v>
       </c>
       <c r="I121" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="J121" t="str">
         <v>High</v>
       </c>
       <c r="K121" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L121" t="str">
         <v>N</v>
@@ -5734,7 +5734,7 @@
         <v>Y</v>
       </c>
       <c r="D122" t="str">
-        <v>2025-04-03</v>
+        <v>2025-04-05</v>
       </c>
       <c r="E122" t="str">
         <v>Y</v>
@@ -5743,7 +5743,7 @@
         <v>Y</v>
       </c>
       <c r="G122">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H122" t="str">
         <v>1-5</v>
@@ -5778,7 +5778,7 @@
         <v>Y</v>
       </c>
       <c r="D123" t="str">
-        <v>2025-04-03</v>
+        <v>2025-04-04</v>
       </c>
       <c r="E123" t="str">
         <v>Y</v>
@@ -5787,7 +5787,7 @@
         <v>Y</v>
       </c>
       <c r="G123">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H123" t="str">
         <v>1-5</v>
@@ -5796,7 +5796,7 @@
         <v>Y</v>
       </c>
       <c r="J123" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K123" t="str">
         <v>N</v>
@@ -5822,28 +5822,28 @@
         <v>Y</v>
       </c>
       <c r="D124" t="str">
-        <v>2025-04-13</v>
+        <v>2025-04-01</v>
       </c>
       <c r="E124" t="str">
         <v>Y</v>
       </c>
       <c r="F124" t="str">
-        <v>N</v>
-      </c>
-      <c r="G124" t="str">
-        <v/>
+        <v>Y</v>
+      </c>
+      <c r="G124">
+        <v>5</v>
       </c>
       <c r="H124" t="str">
         <v>1-5</v>
       </c>
       <c r="I124" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J124" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="K124" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="L124" t="str">
         <v>N</v>
@@ -5866,7 +5866,7 @@
         <v>Y</v>
       </c>
       <c r="D125" t="str">
-        <v>2025-04-05</v>
+        <v>2025-04-17</v>
       </c>
       <c r="E125" t="str">
         <v>Y</v>
@@ -5875,7 +5875,7 @@
         <v>Y</v>
       </c>
       <c r="G125">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H125" t="str">
         <v>1-5</v>
@@ -5884,10 +5884,10 @@
         <v>Y</v>
       </c>
       <c r="J125" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="K125" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L125" t="str">
         <v>N</v>
@@ -5910,16 +5910,16 @@
         <v>Y</v>
       </c>
       <c r="D126" t="str">
-        <v>2025-04-04</v>
+        <v>2025-04-17</v>
       </c>
       <c r="E126" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F126" t="str">
         <v>Y</v>
       </c>
       <c r="G126">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H126" t="str">
         <v>1-5</v>
@@ -5928,10 +5928,10 @@
         <v>Y</v>
       </c>
       <c r="J126" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="K126" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L126" t="str">
         <v>N</v>
@@ -5954,16 +5954,16 @@
         <v>Y</v>
       </c>
       <c r="D127" t="str">
-        <v>2025-04-01</v>
+        <v>2025-04-08</v>
       </c>
       <c r="E127" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F127" t="str">
         <v>Y</v>
       </c>
       <c r="G127">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H127" t="str">
         <v>1-5</v>
@@ -5998,7 +5998,7 @@
         <v>Y</v>
       </c>
       <c r="D128" t="str">
-        <v>2025-04-17</v>
+        <v>2025-04-01</v>
       </c>
       <c r="E128" t="str">
         <v>Y</v>
@@ -6007,7 +6007,7 @@
         <v>Y</v>
       </c>
       <c r="G128">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H128" t="str">
         <v>1-5</v>
@@ -6016,10 +6016,10 @@
         <v>Y</v>
       </c>
       <c r="J128" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="K128" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="L128" t="str">
         <v>N</v>
@@ -6042,28 +6042,28 @@
         <v>Y</v>
       </c>
       <c r="D129" t="str">
-        <v>2025-04-17</v>
+        <v>2025-04-01</v>
       </c>
       <c r="E129" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F129" t="str">
-        <v>Y</v>
-      </c>
-      <c r="G129">
-        <v>5</v>
+        <v>N</v>
+      </c>
+      <c r="G129" t="str">
+        <v/>
       </c>
       <c r="H129" t="str">
         <v>1-5</v>
       </c>
       <c r="I129" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="J129" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="K129" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="L129" t="str">
         <v>N</v>
@@ -6086,16 +6086,16 @@
         <v>Y</v>
       </c>
       <c r="D130" t="str">
-        <v>2025-04-08</v>
+        <v>2025-04-10</v>
       </c>
       <c r="E130" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F130" t="str">
         <v>Y</v>
       </c>
       <c r="G130">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H130" t="str">
         <v>1-5</v>
@@ -6104,19 +6104,19 @@
         <v>Y</v>
       </c>
       <c r="J130" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="K130" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L130" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="M130" t="str">
-        <v/>
+        <v>2026-03-09</v>
       </c>
       <c r="N130" t="str">
-        <v/>
+        <v>Successful</v>
       </c>
     </row>
     <row r="131">
@@ -6130,7 +6130,7 @@
         <v>Y</v>
       </c>
       <c r="D131" t="str">
-        <v>2025-04-01</v>
+        <v>2025-04-09</v>
       </c>
       <c r="E131" t="str">
         <v>Y</v>
@@ -6145,10 +6145,10 @@
         <v>1-5</v>
       </c>
       <c r="I131" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="J131" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="K131" t="str">
         <v>N</v>
@@ -6174,7 +6174,7 @@
         <v>Y</v>
       </c>
       <c r="D132" t="str">
-        <v>2025-04-01</v>
+        <v>2025-04-06</v>
       </c>
       <c r="E132" t="str">
         <v>Y</v>
@@ -6192,10 +6192,10 @@
         <v>N</v>
       </c>
       <c r="J132" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="K132" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L132" t="str">
         <v>N</v>
@@ -6218,7 +6218,7 @@
         <v>Y</v>
       </c>
       <c r="D133" t="str">
-        <v>2025-04-10</v>
+        <v>2025-04-08</v>
       </c>
       <c r="E133" t="str">
         <v>Y</v>
@@ -6236,19 +6236,19 @@
         <v>Y</v>
       </c>
       <c r="J133" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="K133" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="L133" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="M133" t="str">
-        <v>2026-03-09</v>
+        <v/>
       </c>
       <c r="N133" t="str">
-        <v>Successful</v>
+        <v/>
       </c>
     </row>
     <row r="134">
@@ -6262,16 +6262,16 @@
         <v>Y</v>
       </c>
       <c r="D134" t="str">
-        <v>2025-04-09</v>
+        <v>2025-04-01</v>
       </c>
       <c r="E134" t="str">
         <v>Y</v>
       </c>
       <c r="F134" t="str">
-        <v>Y</v>
-      </c>
-      <c r="G134">
-        <v>3</v>
+        <v>N</v>
+      </c>
+      <c r="G134" t="str">
+        <v/>
       </c>
       <c r="H134" t="str">
         <v>1-5</v>
@@ -6306,28 +6306,28 @@
         <v>Y</v>
       </c>
       <c r="D135" t="str">
-        <v>2025-04-06</v>
+        <v>2025-04-02</v>
       </c>
       <c r="E135" t="str">
         <v>Y</v>
       </c>
       <c r="F135" t="str">
-        <v>N</v>
-      </c>
-      <c r="G135" t="str">
-        <v/>
+        <v>Y</v>
+      </c>
+      <c r="G135">
+        <v>4</v>
       </c>
       <c r="H135" t="str">
         <v>1-5</v>
       </c>
       <c r="I135" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J135" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="K135" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="L135" t="str">
         <v>N</v>
@@ -6350,7 +6350,7 @@
         <v>Y</v>
       </c>
       <c r="D136" t="str">
-        <v>2025-04-08</v>
+        <v>2025-04-13</v>
       </c>
       <c r="E136" t="str">
         <v>Y</v>
@@ -6368,10 +6368,10 @@
         <v>Y</v>
       </c>
       <c r="J136" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="K136" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L136" t="str">
         <v>N</v>
